--- a/task177/golden/pool_90dpd_forecast.xlsx
+++ b/task177/golden/pool_90dpd_forecast.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1146,22 +1146,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CPN-MF-07 sections 2 and 3, on the bureau's portfolio review at the cut-off</t>
+          <t>Members' repayment from 1 January 2027 taken as in the assignor's experience before the cyclone of 16 October 2026 (term sheet clause 12)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CPN-MF-07 sections 2 and 3, on the bureau's portfolio review at the cut-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Forecast to the nearest 100 loans; principal in INR lakh to one decimal</t>
         </is>
